--- a/technical_assessment_by_job/questions/python_questions.xlsx
+++ b/technical_assessment_by_job/questions/python_questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai_ws\technical_assessment_by_job\questions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai\codex_projects\technical_assessment_by_job\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{584A530F-C565-4538-A441-F656DAAFB91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB3D9FD-920B-415D-A144-1BF6B9104349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{19C96228-82AB-4F67-ABF6-AAD99FBF6CD0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="466">
   <si>
     <t>#</t>
   </si>
@@ -7872,6 +7872,65 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> to identify bottlenecks in execution time.</t>
+    </r>
+  </si>
+  <si>
+    <t>What is a "virtual environment" in Python and why use it?</t>
+  </si>
+  <si>
+    <t>It isolates project dependencies to avoid conflicts with system-level packages.</t>
+  </si>
+  <si>
+    <t>How do you manage Python dependencies in a Docker image?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Using a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>requirements.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> file and running </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>pip install</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> during the build phase</t>
     </r>
   </si>
 </sst>
@@ -7879,7 +7938,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7911,6 +7970,12 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -8306,11 +8371,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E12BB6F-5793-4644-B4E8-9C2C633CBE33}">
-  <dimension ref="A1:C231"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr defaultColWidth="164.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="123.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10855,6 +10920,22 @@
         <v>461</v>
       </c>
     </row>
+    <row r="232" spans="1:3">
+      <c r="B232" t="s">
+        <v>462</v>
+      </c>
+      <c r="C232" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="B233" t="s">
+        <v>464</v>
+      </c>
+      <c r="C233" t="s">
+        <v>465</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
